--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81390415</v>
+        <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
+        <v>109906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400 m N Lannamärkets vägkors, Sk</t>
+          <t>Brammarp,1,1 km NV, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372476.5763448753</v>
+        <v>372501</v>
       </c>
       <c r="R2" t="n">
-        <v>6248653.039502296</v>
+        <v>6248645</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +752,24 @@
           <t>Hjärnarp</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Äng-0218</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>18 ex i knopp inom 10m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +783,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Bäck öster om E6</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -785,10 +794,131 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>81390415</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106964</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>400 m N Lannamärkets vägkors, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>372476.5763448753</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6248653.039502296</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Mats Gustafsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
         </is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>109906</v>
+        <v>110092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>110092</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>VU</t>
